--- a/STRATBOOK_FINAL.xlsx
+++ b/STRATBOOK_FINAL.xlsx
@@ -297,7 +297,7 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Сводная таблица    •    Обновлено: 25.09.2026 11:20</t>
+          <t xml:space="preserve">Сводная таблица    •    Обновлено: 25.09.2026 11:34</t>
         </is>
       </c>
       <c r="B2" s="2"/>
@@ -949,7 +949,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Раунды: 144    •    Пистолетки: 6    •    Спавнов: 66    •    Стенок: 10    •    Гранат: 5    •    25.09.2026 11:20</t>
+          <t xml:space="preserve">Раунды: 144    •    Пистолетки: 6    •    Спавнов: 66    •    Стенок: 10    •    Гранат: 5    •    25.09.2026 11:34</t>
         </is>
       </c>
       <c r="B2" s="2"/>
@@ -6397,7 +6397,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Раунды: 54    •    Пистолетки: 2    •    Спавнов: 27    •    Стенок: 0    •    Гранат: 0    •    25.09.2026 11:20</t>
+          <t xml:space="preserve">Раунды: 54    •    Пистолетки: 2    •    Спавнов: 27    •    Стенок: 0    •    Гранат: 0    •    25.09.2026 11:34</t>
         </is>
       </c>
       <c r="B2" s="2"/>
@@ -8421,7 +8421,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Раунды: 80    •    Пистолетки: 3    •    Спавнов: 0    •    Стенок: 0    •    Гранат: 2    •    25.09.2026 11:20</t>
+          <t xml:space="preserve">Раунды: 80    •    Пистолетки: 3    •    Спавнов: 0    •    Стенок: 0    •    Гранат: 2    •    25.09.2026 11:34</t>
         </is>
       </c>
       <c r="B2" s="2"/>
@@ -10291,7 +10291,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Раунды: 140    •    Пистолетки: 6    •    Спавнов: 30    •    Стенок: 0    •    Гранат: 0    •    25.09.2026 11:20</t>
+          <t xml:space="preserve">Раунды: 140    •    Пистолетки: 6    •    Спавнов: 30    •    Стенок: 0    •    Гранат: 0    •    25.09.2026 11:34</t>
         </is>
       </c>
       <c r="B2" s="2"/>
@@ -14067,7 +14067,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Раунды: 95    •    Пистолетки: 4    •    Спавнов: 5    •    Стенок: 0    •    Гранат: 6    •    25.09.2026 11:20</t>
+          <t xml:space="preserve">Раунды: 95    •    Пистолетки: 4    •    Спавнов: 5    •    Стенок: 0    •    Гранат: 6    •    25.09.2026 11:34</t>
         </is>
       </c>
       <c r="B2" s="2"/>
@@ -16584,7 +16584,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Раунды: 9    •    Пистолетки: 0    •    Спавнов: 0    •    Стенок: 0    •    Гранат: 0    •    25.09.2026 11:20</t>
+          <t xml:space="preserve">Раунды: 9    •    Пистолетки: 0    •    Спавнов: 0    •    Стенок: 0    •    Гранат: 0    •    25.09.2026 11:34</t>
         </is>
       </c>
       <c r="B2" s="2"/>
@@ -16901,7 +16901,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Раунды: 25    •    Пистолетки: 0    •    Спавнов: 0    •    Стенок: 0    •    Гранат: 1    •    25.09.2026 11:20</t>
+          <t xml:space="preserve">Раунды: 25    •    Пистолетки: 0    •    Спавнов: 0    •    Стенок: 0    •    Гранат: 1    •    25.09.2026 11:34</t>
         </is>
       </c>
       <c r="B2" s="2"/>
@@ -17587,7 +17587,7 @@
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Раунды: 10    •    Пистолетки: 2    •    Спавнов: 0    •    Стенок: 0    •    Гранат: 0    •    25.09.2026 11:20</t>
+          <t xml:space="preserve">Раунды: 10    •    Пистолетки: 2    •    Спавнов: 0    •    Стенок: 0    •    Гранат: 0    •    25.09.2026 11:34</t>
         </is>
       </c>
       <c r="B2" s="2"/>
